--- a/public/excel/product/Giá xà gồ C, Z.xlsx
+++ b/public/excel/product/Giá xà gồ C, Z.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="108">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">C 80 x 40 x 15 x 1.8 x 6m</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">C 80 x 40 x 15 x 2.0 x 6m</t>
@@ -574,7 +580,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.71"/>
@@ -611,10 +617,13 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>6</v>
@@ -635,15 +644,18 @@
         <v>196.323</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>6</v>
@@ -664,15 +676,18 @@
         <v>236.596</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>6</v>
@@ -693,15 +708,18 @@
         <v>266.496</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>6</v>
@@ -722,15 +740,18 @@
         <v>265.196</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>6</v>
@@ -751,15 +772,18 @@
         <v>285.996</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>6</v>
@@ -780,15 +804,18 @@
         <v>342.285</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>6</v>
@@ -809,15 +836,18 @@
         <v>509.566</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>6</v>
@@ -838,15 +868,18 @@
         <v>229.706</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>6</v>
@@ -867,15 +900,18 @@
         <v>302.375</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>6</v>
@@ -896,15 +932,18 @@
         <v>470.333</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>6</v>
@@ -925,15 +964,18 @@
         <v>225.287</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>6</v>
@@ -954,15 +996,18 @@
         <v>268.056</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>6</v>
@@ -983,15 +1028,18 @@
         <v>195.387</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>6</v>
@@ -1012,15 +1060,18 @@
         <v>324.085</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>6</v>
@@ -1041,15 +1092,18 @@
         <v>306.535</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>6</v>
@@ -1070,15 +1124,18 @@
         <v>263.636</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>6</v>
@@ -1099,15 +1156,18 @@
         <v>384.664</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>6</v>
@@ -1128,15 +1188,18 @@
         <v>434.063</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>6</v>
@@ -1157,15 +1220,18 @@
         <v>549.242</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>6</v>
@@ -1186,15 +1252,18 @@
         <v>339.555</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>6</v>
@@ -1215,15 +1284,18 @@
         <v>375.694</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>6</v>
@@ -1244,15 +1316,18 @@
         <v>411.574</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>6</v>
@@ -1273,15 +1348,18 @@
         <v>464.743</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>6</v>
@@ -1302,15 +1380,18 @@
         <v>588.371</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>6</v>
@@ -1331,15 +1412,18 @@
         <v>366.854</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>6</v>
@@ -1360,15 +1444,18 @@
         <v>351.385</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>6</v>
@@ -1389,15 +1476,18 @@
         <v>384.664</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>6</v>
@@ -1418,15 +1508,18 @@
         <v>434.063</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>6</v>
@@ -1447,15 +1540,18 @@
         <v>549.242</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>6</v>
@@ -1476,15 +1572,18 @@
         <v>372.964</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>6</v>
@@ -1505,15 +1604,18 @@
         <v>412.614</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>6</v>
@@ -1534,15 +1636,18 @@
         <v>464.743</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>6</v>
@@ -1563,15 +1668,18 @@
         <v>510.632</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>6</v>
@@ -1592,15 +1700,18 @@
         <v>647.13</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>6</v>
@@ -1621,15 +1732,18 @@
         <v>405.854</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>6</v>
@@ -1650,15 +1764,18 @@
         <v>449.273</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>6</v>
@@ -1679,15 +1796,18 @@
         <v>492.432</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>6</v>
@@ -1708,15 +1828,18 @@
         <v>556.521</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>6</v>
@@ -1737,15 +1860,18 @@
         <v>706.019</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>6</v>
@@ -1766,15 +1892,18 @@
         <v>485.933</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>6</v>
@@ -1795,15 +1924,18 @@
         <v>556.131</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B43" s="3" t="n">
         <v>6</v>
@@ -1824,15 +1956,18 @@
         <v>602.541</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B44" s="3" t="n">
         <v>6</v>
@@ -1853,15 +1988,18 @@
         <v>664.94</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B45" s="3" t="n">
         <v>6</v>
@@ -1882,15 +2020,18 @@
         <v>764.778</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B46" s="3" t="n">
         <v>6</v>
@@ -1911,15 +2052,18 @@
         <v>534.942</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="3" t="n">
         <v>6</v>
@@ -1940,15 +2084,18 @@
         <v>612.551</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B48" s="3" t="n">
         <v>6</v>
@@ -1969,15 +2116,18 @@
         <v>670.01</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B49" s="3" t="n">
         <v>6</v>
@@ -1998,15 +2148,18 @@
         <v>790.388</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B50" s="3" t="n">
         <v>6</v>
@@ -2027,15 +2180,18 @@
         <v>843.167</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B51" s="3" t="n">
         <v>6</v>
@@ -2056,15 +2212,18 @@
         <v>580.311</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B52" s="3" t="n">
         <v>6</v>
@@ -2085,15 +2244,18 @@
         <v>682.879</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B53" s="3" t="n">
         <v>6</v>
@@ -2114,15 +2276,18 @@
         <v>740.209</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B54" s="3" t="n">
         <v>6</v>
@@ -2143,15 +2308,18 @@
         <v>882.296</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B55" s="3" t="n">
         <v>6</v>
@@ -2172,15 +2340,18 @@
         <v>941.056</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B56" s="3" t="n">
         <v>6</v>
@@ -2201,15 +2372,18 @@
         <v>280.146</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B57" s="3" t="n">
         <v>6</v>
@@ -2230,15 +2404,18 @@
         <v>336.175</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B58" s="3" t="n">
         <v>6</v>
@@ -2259,15 +2436,18 @@
         <v>373.614</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B59" s="3" t="n">
         <v>6</v>
@@ -2288,15 +2468,18 @@
         <v>466.953</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B60" s="3" t="n">
         <v>0</v>
@@ -2317,15 +2500,18 @@
         <v>560.291</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B61" s="3" t="n">
         <v>6</v>
@@ -2346,15 +2532,18 @@
         <v>597.731</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B62" s="3" t="n">
         <v>6</v>
@@ -2375,15 +2564,18 @@
         <v>307.705</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B63" s="3" t="n">
         <v>6</v>
@@ -2404,15 +2596,18 @@
         <v>368.934</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B64" s="3" t="n">
         <v>6</v>
@@ -2433,15 +2628,18 @@
         <v>410.274</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B65" s="3" t="n">
         <v>6</v>
@@ -2462,15 +2660,18 @@
         <v>471.763</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B66" s="3" t="n">
         <v>6</v>
@@ -2491,15 +2692,18 @@
         <v>512.842</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B67" s="3" t="n">
         <v>6</v>
@@ -2520,15 +2724,18 @@
         <v>615.411</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B68" s="3" t="n">
         <v>6</v>
@@ -2549,15 +2756,18 @@
         <v>656.36</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B69" s="3" t="n">
         <v>6</v>
@@ -2578,15 +2788,18 @@
         <v>307.705</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B70" s="3" t="n">
         <v>6</v>
@@ -2607,15 +2820,18 @@
         <v>369.194</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B71" s="3" t="n">
         <v>6</v>
@@ -2636,15 +2852,18 @@
         <v>410.274</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B72" s="3" t="n">
         <v>6</v>
@@ -2665,15 +2884,18 @@
         <v>471.763</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B73" s="3" t="n">
         <v>6</v>
@@ -2694,15 +2916,18 @@
         <v>512.842</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B74" s="3" t="n">
         <v>6</v>
@@ -2723,15 +2948,18 @@
         <v>615.411</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B75" s="3" t="n">
         <v>6</v>
@@ -2752,15 +2980,18 @@
         <v>656.36</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B76" s="3" t="n">
         <v>6</v>
@@ -2781,15 +3012,18 @@
         <v>326.035</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B77" s="3" t="n">
         <v>6</v>
@@ -2810,15 +3044,18 @@
         <v>391.294</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B78" s="3" t="n">
         <v>6</v>
@@ -2839,15 +3076,18 @@
         <v>447.843</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B79" s="3" t="n">
         <v>6</v>
@@ -2868,15 +3108,18 @@
         <v>300.035</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B80" s="3" t="n">
         <v>6</v>
@@ -2897,15 +3140,18 @@
         <v>543.522</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B81" s="3" t="n">
         <v>6</v>
@@ -2926,15 +3172,18 @@
         <v>652.07</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B82" s="3" t="n">
         <v>6</v>
@@ -2955,15 +3204,18 @@
         <v>695.619</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B83" s="3" t="n">
         <v>6</v>
@@ -2984,15 +3236,18 @@
         <v>393.114</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B84" s="3" t="n">
         <v>6</v>
@@ -3013,15 +3268,18 @@
         <v>468.383</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B85" s="3" t="n">
         <v>6</v>
@@ -3042,15 +3300,18 @@
         <v>520.512</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B86" s="3" t="n">
         <v>6</v>
@@ -3071,15 +3332,18 @@
         <v>598.511</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B87" s="3" t="n">
         <v>6</v>
@@ -3100,15 +3364,18 @@
         <v>650.64</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B88" s="3" t="n">
         <v>6</v>
@@ -3129,15 +3396,18 @@
         <v>780.768</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B89" s="3" t="n">
         <v>6</v>
@@ -3158,15 +3428,18 @@
         <v>832.767</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B90" s="3" t="n">
         <v>6</v>
@@ -3187,15 +3460,18 @@
         <v>436.273</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B91" s="3" t="n">
         <v>6</v>
@@ -3216,15 +3492,18 @@
         <v>522.982</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B92" s="3" t="n">
         <v>6</v>
@@ -3245,15 +3524,18 @@
         <v>581.741</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B93" s="3" t="n">
         <v>6</v>
@@ -3274,15 +3556,18 @@
         <v>668.97</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B94" s="3" t="n">
         <v>6</v>
@@ -3303,15 +3588,18 @@
         <v>727.209</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B95" s="3" t="n">
         <v>6</v>
@@ -3332,15 +3620,18 @@
         <v>872.547</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B96" s="3" t="n">
         <v>6</v>
@@ -3361,10 +3652,13 @@
         <v>930.656</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
